--- a/data/trans_orig/IP25B_1_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP25B_1_R-Edad-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>872</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7519</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1501</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8172</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49503</t>
+          <t>49370</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50857</t>
+          <t>50476</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57470</t>
+          <t>57504</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101777</t>
+          <t>101159</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>108809</t>
+          <t>108448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7683</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>18714</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17379</t>
+          <t>17027</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35087</t>
+          <t>34009</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28632</t>
+          <t>27561</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47973</t>
+          <t>47927</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>135571</t>
+          <t>136338</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>147369</t>
+          <t>147588</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>146973</t>
+          <t>148051</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>164681</t>
+          <t>165033</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>289139</t>
+          <t>289185</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>308480</t>
+          <t>309551</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,82%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32640</t>
+          <t>32264</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54381</t>
+          <t>54047</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28966</t>
+          <t>28989</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48693</t>
+          <t>49683</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67157</t>
+          <t>68245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97995</t>
+          <t>99201</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>118691</t>
+          <t>119025</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>140432</t>
+          <t>140808</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>163797</t>
+          <t>162807</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>183524</t>
+          <t>183501</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>287568</t>
+          <t>286362</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>318406</t>
+          <t>317318</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,3%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81482</t>
+          <t>81427</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>155340</t>
+          <t>154236</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97668</t>
+          <t>98950</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>143095</t>
+          <t>144499</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>191294</t>
+          <t>192634</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>277472</t>
+          <t>274903</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>47,94%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>115957</t>
+          <t>117061</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>189815</t>
+          <t>189870</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>159040</t>
+          <t>157636</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>204467</t>
+          <t>203185</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>295960</t>
+          <t>298529</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>382138</t>
+          <t>380798</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,41%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>132180</t>
+          <t>131679</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>228954</t>
+          <t>231542</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>156383</t>
+          <t>157692</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>214708</t>
+          <t>216130</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>305178</t>
+          <t>306744</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>420889</t>
+          <t>417915</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>422040</t>
+          <t>419452</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>518814</t>
+          <t>519315</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>540352</t>
+          <t>538930</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>598677</t>
+          <t>597368</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>985166</t>
+          <t>988140</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1100877</t>
+          <t>1099311</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,18%</t>
         </is>
       </c>
     </row>
